--- a/ConfigExporter/xlsx/game_prefab.xlsx
+++ b/ConfigExporter/xlsx/game_prefab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06467188-75D5-4CC0-916C-D71005A93107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3978581-6B03-4C1E-A95D-22E2C5DC0364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="6120" windowWidth="29205" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8115" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_prefab" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>eventSystem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 全局默认加载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IngameDebugConsole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plugins/IngameDebugConsole/IngameDebugConsole</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,10 +442,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="17.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="56.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -485,9 +498,22 @@
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/game_prefab.xlsx
+++ b/ConfigExporter/xlsx/game_prefab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3978581-6B03-4C1E-A95D-22E2C5DC0364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2A8EC9-46B7-4FA3-80DE-6EF2F06EA406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8115" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8235" yWindow="3270" windowWidth="22170" windowHeight="16605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_prefab" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,6 +80,14 @@
   </si>
   <si>
     <t>Plugins/IngameDebugConsole/IngameDebugConsole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_LootDrop_Blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Models/VFX/FX_LootDrop_Blue</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.875" style="1" customWidth="1"/>
@@ -516,6 +524,15 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigExporter/xlsx/game_prefab.xlsx
+++ b/ConfigExporter/xlsx/game_prefab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2A8EC9-46B7-4FA3-80DE-6EF2F06EA406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61A47FC-5FF3-46ED-BB3C-1FF84E53F1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8235" yWindow="3270" windowWidth="22170" windowHeight="16605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8565" yWindow="1170" windowWidth="22170" windowHeight="16605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_prefab" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,22 @@
   </si>
   <si>
     <t>Models/VFX/FX_LootDrop_Blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChessBlack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Models/Chess/ChessBlack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChessWhite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Models/Chess/ChessWhite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -450,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.875" style="1" customWidth="1"/>
@@ -533,6 +549,24 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
